--- a/artfynd/A 14539-2026 artfynd.xlsx
+++ b/artfynd/A 14539-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY117"/>
+  <dimension ref="A1:AY122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133438077</v>
+        <v>133435975</v>
       </c>
       <c r="B2" t="n">
-        <v>57975</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578189</v>
+        <v>578170</v>
       </c>
       <c r="R2" t="n">
-        <v>7068967</v>
+        <v>7069072</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,24 +743,9 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,61 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133430713</v>
+        <v>133436287</v>
       </c>
       <c r="B3" t="n">
-        <v>99180</v>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grelsmyran, Grelsmyran, Ång</t>
+          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578421</v>
+        <v>578134</v>
       </c>
       <c r="R3" t="n">
-        <v>7068942</v>
+        <v>7069094</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -893,45 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133436474</v>
+        <v>133430250</v>
       </c>
       <c r="B4" t="n">
-        <v>98045</v>
+        <v>91970</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
+          <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578142</v>
+        <v>578387</v>
       </c>
       <c r="R4" t="n">
-        <v>7069100</v>
+        <v>7068861</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -990,49 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133429893</v>
+        <v>133429701</v>
       </c>
       <c r="B5" t="n">
-        <v>99180</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578469</v>
+        <v>578473</v>
       </c>
       <c r="R5" t="n">
-        <v>7068830</v>
+        <v>7068808</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1091,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133438295</v>
+        <v>133430504</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1102,39 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578362</v>
+        <v>578403</v>
       </c>
       <c r="R6" t="n">
-        <v>7068822</v>
+        <v>7068862</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1167,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,45 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133435938</v>
+        <v>133433807</v>
       </c>
       <c r="B7" t="n">
-        <v>97293</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
+          <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578170</v>
+        <v>578434</v>
       </c>
       <c r="R7" t="n">
-        <v>7069073</v>
+        <v>7068981</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1295,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133438750</v>
+        <v>133434590</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1306,42 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578442</v>
+        <v>578381</v>
       </c>
       <c r="R8" t="n">
-        <v>7068773</v>
+        <v>7069074</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1368,14 +1325,19 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1390,22 +1352,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133437997</v>
+        <v>133434805</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1413,42 +1375,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
+          <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578178</v>
+        <v>578367</v>
       </c>
       <c r="R9" t="n">
-        <v>7068977</v>
+        <v>7069065</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1475,24 +1432,9 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1507,22 +1449,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133438778</v>
+        <v>133436291</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>91974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1530,42 +1472,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grelsmyran, Grelsmyran, Ång</t>
+          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578454</v>
+        <v>578138</v>
       </c>
       <c r="R10" t="n">
-        <v>7068761</v>
+        <v>7069103</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1592,14 +1529,19 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1614,44 +1556,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133432869</v>
+        <v>133435067</v>
       </c>
       <c r="B11" t="n">
-        <v>80474</v>
+        <v>91985</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1661,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578371</v>
+        <v>578303</v>
       </c>
       <c r="R11" t="n">
-        <v>7068956</v>
+        <v>7069048</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1696,7 +1638,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1706,7 +1648,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1736,7 +1678,7 @@
         <v>133430066</v>
       </c>
       <c r="B12" t="n">
-        <v>83208</v>
+        <v>83222</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133432266</v>
+        <v>133432171</v>
       </c>
       <c r="B13" t="n">
-        <v>80474</v>
+        <v>83222</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1875,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578376</v>
+        <v>578390</v>
       </c>
       <c r="R13" t="n">
-        <v>7068960</v>
+        <v>7068946</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1910,7 +1852,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1920,7 +1862,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1947,49 +1889,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133429928</v>
+        <v>133433950</v>
       </c>
       <c r="B14" t="n">
-        <v>99180</v>
+        <v>83222</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578452</v>
+        <v>578437</v>
       </c>
       <c r="R14" t="n">
-        <v>7068835</v>
+        <v>7068980</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,7 +1959,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2031,7 +1969,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2058,32 +1996,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133434892</v>
+        <v>133433926</v>
       </c>
       <c r="B15" t="n">
-        <v>80474</v>
+        <v>92318</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,13 +2031,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578330</v>
+        <v>578399</v>
       </c>
       <c r="R15" t="n">
-        <v>7069066</v>
+        <v>7068854</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2126,19 +2064,9 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,22 +2081,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133430665</v>
+        <v>133429555</v>
       </c>
       <c r="B16" t="n">
-        <v>79359</v>
+        <v>80489</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2176,21 +2104,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2200,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578441</v>
+        <v>578443</v>
       </c>
       <c r="R16" t="n">
-        <v>7068938</v>
+        <v>7068790</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2262,52 +2190,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133432167</v>
+        <v>133434509</v>
       </c>
       <c r="B17" t="n">
-        <v>99180</v>
+        <v>80489</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578386</v>
+        <v>578389</v>
       </c>
       <c r="R17" t="n">
-        <v>7068948</v>
+        <v>7069082</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2334,9 +2258,19 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2351,22 +2285,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133435594</v>
+        <v>133436760</v>
       </c>
       <c r="B18" t="n">
-        <v>79359</v>
+        <v>80489</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2374,37 +2308,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Grelsmyran, Grelsmyran, Ång</t>
+          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578248</v>
+        <v>578226</v>
       </c>
       <c r="R18" t="n">
-        <v>7069051</v>
+        <v>7069161</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2431,9 +2365,19 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2448,22 +2392,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133435383</v>
+        <v>133433583</v>
       </c>
       <c r="B19" t="n">
-        <v>93256</v>
+        <v>97308</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2471,21 +2415,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2495,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>578292</v>
+        <v>578420</v>
       </c>
       <c r="R19" t="n">
-        <v>7069074</v>
+        <v>7068972</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2557,45 +2501,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133437259</v>
+        <v>133435938</v>
       </c>
       <c r="B20" t="n">
-        <v>79359</v>
+        <v>97308</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Grelsmyran, Grelsmyran, Ång</t>
+          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>578265</v>
+        <v>578170</v>
       </c>
       <c r="R20" t="n">
-        <v>7069115</v>
+        <v>7069073</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2654,10 +2598,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133429497</v>
+        <v>133435383</v>
       </c>
       <c r="B21" t="n">
-        <v>57975</v>
+        <v>93271</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2665,39 +2609,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>578428</v>
+        <v>578292</v>
       </c>
       <c r="R21" t="n">
-        <v>7068775</v>
+        <v>7069074</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2730,11 +2669,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tre granar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2761,10 +2695,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133437670</v>
+        <v>133435534</v>
       </c>
       <c r="B22" t="n">
-        <v>79359</v>
+        <v>93271</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2772,34 +2706,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
+          <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>578177</v>
+        <v>578265</v>
       </c>
       <c r="R22" t="n">
-        <v>7069034</v>
+        <v>7069037</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2858,45 +2792,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133429944</v>
+        <v>133437423</v>
       </c>
       <c r="B23" t="n">
-        <v>80479</v>
+        <v>93271</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Grelsmyran, Grelsmyran, Ång</t>
+          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578460</v>
+        <v>578202</v>
       </c>
       <c r="R23" t="n">
-        <v>7068837</v>
+        <v>7069041</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2955,10 +2889,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133434904</v>
+        <v>133432574</v>
       </c>
       <c r="B24" t="n">
-        <v>80478</v>
+        <v>91937</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2966,21 +2900,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6461</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2990,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578359</v>
+        <v>578399</v>
       </c>
       <c r="R24" t="n">
-        <v>7069082</v>
+        <v>7068956</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3055,7 +2989,7 @@
         <v>133433861</v>
       </c>
       <c r="B25" t="n">
-        <v>91922</v>
+        <v>91937</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3149,45 +3083,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133436760</v>
+        <v>133429594</v>
       </c>
       <c r="B26" t="n">
-        <v>80475</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
+          <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578226</v>
+        <v>578438</v>
       </c>
       <c r="R26" t="n">
-        <v>7069161</v>
+        <v>7068789</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3219,7 +3153,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3229,7 +3163,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3256,50 +3190,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133438237</v>
+        <v>133430270</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>578345</v>
+        <v>578405</v>
       </c>
       <c r="R27" t="n">
-        <v>7068862</v>
+        <v>7068842</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3332,11 +3261,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3363,50 +3287,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133438615</v>
+        <v>133430444</v>
       </c>
       <c r="B28" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>578397</v>
+        <v>578400</v>
       </c>
       <c r="R28" t="n">
-        <v>7068804</v>
+        <v>7068873</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3439,11 +3358,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3470,14 +3384,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133433648</v>
+        <v>133430665</v>
       </c>
       <c r="B29" t="n">
-        <v>79359</v>
+        <v>79373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3505,10 +3419,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>578420</v>
+        <v>578441</v>
       </c>
       <c r="R29" t="n">
-        <v>7068974</v>
+        <v>7068938</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3567,50 +3481,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133438270</v>
+        <v>133430717</v>
       </c>
       <c r="B30" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>578349</v>
+        <v>578436</v>
       </c>
       <c r="R30" t="n">
-        <v>7068845</v>
+        <v>7068915</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,7 +3551,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3652,12 +3561,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3684,53 +3588,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133438451</v>
+        <v>133431225</v>
       </c>
       <c r="B31" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>578375</v>
+        <v>578436</v>
       </c>
       <c r="R31" t="n">
-        <v>7068798</v>
+        <v>7068937</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3757,14 +3656,19 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3779,26 +3683,26 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133436867</v>
+        <v>133432193</v>
       </c>
       <c r="B32" t="n">
-        <v>79359</v>
+        <v>79373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3822,17 +3726,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
+          <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>578230</v>
+        <v>578384</v>
       </c>
       <c r="R32" t="n">
-        <v>7069144</v>
+        <v>7068959</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3859,19 +3763,9 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3886,65 +3780,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133429367</v>
+        <v>133433648</v>
       </c>
       <c r="B33" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>578434</v>
+        <v>578420</v>
       </c>
       <c r="R33" t="n">
-        <v>7068778</v>
+        <v>7068974</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3971,24 +3860,9 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4003,57 +3877,57 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133437086</v>
+        <v>133433999</v>
       </c>
       <c r="B34" t="n">
-        <v>79116</v>
+        <v>79373</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
+          <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578212</v>
+        <v>578377</v>
       </c>
       <c r="R34" t="n">
-        <v>7069124</v>
+        <v>7068960</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4112,32 +3986,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133434805</v>
+        <v>133434232</v>
       </c>
       <c r="B35" t="n">
-        <v>91959</v>
+        <v>79373</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4147,10 +4021,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578367</v>
+        <v>578401</v>
       </c>
       <c r="R35" t="n">
-        <v>7069065</v>
+        <v>7069051</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4209,32 +4083,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133430374</v>
+        <v>133434261</v>
       </c>
       <c r="B36" t="n">
-        <v>80474</v>
+        <v>79373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4244,13 +4118,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578394</v>
+        <v>578409</v>
       </c>
       <c r="R36" t="n">
-        <v>7068863</v>
+        <v>7069061</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4277,9 +4151,19 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4294,57 +4178,57 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133435975</v>
+        <v>133434766</v>
       </c>
       <c r="B37" t="n">
-        <v>92230</v>
+        <v>79373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
+          <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578170</v>
+        <v>578368</v>
       </c>
       <c r="R37" t="n">
-        <v>7069072</v>
+        <v>7069064</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4403,27 +4287,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133436778</v>
+        <v>133435402</v>
       </c>
       <c r="B38" t="n">
-        <v>80485</v>
+        <v>79373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4434,14 +4318,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
+          <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578226</v>
+        <v>578289</v>
       </c>
       <c r="R38" t="n">
-        <v>7069160</v>
+        <v>7069077</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4500,32 +4384,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133430065</v>
+        <v>133435485</v>
       </c>
       <c r="B39" t="n">
-        <v>80474</v>
+        <v>79373</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4535,10 +4419,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578420</v>
+        <v>578285</v>
       </c>
       <c r="R39" t="n">
-        <v>7068858</v>
+        <v>7069069</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4597,45 +4481,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133436792</v>
+        <v>133435594</v>
       </c>
       <c r="B40" t="n">
-        <v>80479</v>
+        <v>79373</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
+          <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578224</v>
+        <v>578248</v>
       </c>
       <c r="R40" t="n">
-        <v>7069161</v>
+        <v>7069051</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4694,14 +4578,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133438247</v>
+        <v>133435652</v>
       </c>
       <c r="B41" t="n">
-        <v>79359</v>
+        <v>79373</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4725,17 +4609,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Grelsmyran, Grelsmyran, Ång</t>
+          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578353</v>
+        <v>578216</v>
       </c>
       <c r="R41" t="n">
-        <v>7068883</v>
+        <v>7069068</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4762,9 +4646,19 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4779,44 +4673,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133436758</v>
+        <v>133435901</v>
       </c>
       <c r="B42" t="n">
-        <v>80474</v>
+        <v>79373</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4826,10 +4720,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578224</v>
+        <v>578190</v>
       </c>
       <c r="R42" t="n">
-        <v>7069159</v>
+        <v>7069071</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4888,48 +4782,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133433493</v>
+        <v>133435992</v>
       </c>
       <c r="B43" t="n">
-        <v>80474</v>
+        <v>79373</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Grelsmyran, Grelsmyran, Ång</t>
+          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578396</v>
+        <v>578161</v>
       </c>
       <c r="R43" t="n">
-        <v>7068978</v>
+        <v>7069056</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4956,9 +4850,19 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4973,65 +4877,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133437836</v>
+        <v>133436867</v>
       </c>
       <c r="B44" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578155</v>
+        <v>578230</v>
       </c>
       <c r="R44" t="n">
-        <v>7069003</v>
+        <v>7069144</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5058,14 +4957,19 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5080,44 +4984,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133433807</v>
+        <v>133437259</v>
       </c>
       <c r="B45" t="n">
-        <v>91959</v>
+        <v>79373</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5127,10 +5031,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578434</v>
+        <v>578265</v>
       </c>
       <c r="R45" t="n">
-        <v>7068981</v>
+        <v>7069115</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5189,14 +5093,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133430444</v>
+        <v>133437670</v>
       </c>
       <c r="B46" t="n">
-        <v>79359</v>
+        <v>79373</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5220,14 +5124,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Grelsmyran, Grelsmyran, Ång</t>
+          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578400</v>
+        <v>578177</v>
       </c>
       <c r="R46" t="n">
-        <v>7068873</v>
+        <v>7069034</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5286,14 +5190,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133435485</v>
+        <v>133437687</v>
       </c>
       <c r="B47" t="n">
-        <v>79359</v>
+        <v>79373</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5317,14 +5221,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Grelsmyran, Grelsmyran, Ång</t>
+          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>578285</v>
+        <v>578173</v>
       </c>
       <c r="R47" t="n">
-        <v>7069069</v>
+        <v>7069031</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5383,48 +5287,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133431209</v>
+        <v>133437840</v>
       </c>
       <c r="B48" t="n">
-        <v>80474</v>
+        <v>79373</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Grelsmyran, Grelsmyran, Ång</t>
+          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>578421</v>
+        <v>578136</v>
       </c>
       <c r="R48" t="n">
-        <v>7068947</v>
+        <v>7069035</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5451,9 +5355,19 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5468,57 +5382,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133433039</v>
+        <v>133437851</v>
       </c>
       <c r="B49" t="n">
-        <v>80474</v>
+        <v>79373</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Grelsmyran, Grelsmyran, Ång</t>
+          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>578409</v>
+        <v>578141</v>
       </c>
       <c r="R49" t="n">
-        <v>7068983</v>
+        <v>7069003</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5577,32 +5491,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133435067</v>
+        <v>133438078</v>
       </c>
       <c r="B50" t="n">
-        <v>91970</v>
+        <v>79373</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5612,13 +5526,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>578303</v>
+        <v>578240</v>
       </c>
       <c r="R50" t="n">
-        <v>7069048</v>
+        <v>7068968</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5645,19 +5559,9 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>14:37</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5672,60 +5576,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133437114</v>
+        <v>133438247</v>
       </c>
       <c r="B51" t="n">
-        <v>79978</v>
+        <v>79373</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
+          <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>578213</v>
+        <v>578353</v>
       </c>
       <c r="R51" t="n">
-        <v>7069129</v>
+        <v>7068883</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5752,19 +5656,9 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5779,57 +5673,57 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133433926</v>
+        <v>133435661</v>
       </c>
       <c r="B52" t="n">
-        <v>92303</v>
+        <v>78776</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2062</v>
+        <v>6437</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Grelsmyran, Grelsmyran, Ång</t>
+          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>578399</v>
+        <v>578205</v>
       </c>
       <c r="R52" t="n">
-        <v>7068854</v>
+        <v>7069057</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5888,32 +5782,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133433583</v>
+        <v>133431175</v>
       </c>
       <c r="B53" t="n">
-        <v>97293</v>
+        <v>79130</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2869</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5923,13 +5817,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>578420</v>
+        <v>578457</v>
       </c>
       <c r="R53" t="n">
-        <v>7068972</v>
+        <v>7068932</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5956,9 +5850,19 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5973,22 +5877,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133429982</v>
+        <v>133437086</v>
       </c>
       <c r="B54" t="n">
-        <v>80474</v>
+        <v>79130</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5996,37 +5900,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Grelsmyran, Grelsmyran, Ång</t>
+          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>578431</v>
+        <v>578212</v>
       </c>
       <c r="R54" t="n">
-        <v>7068866</v>
+        <v>7069124</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6053,19 +5957,9 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6080,60 +5974,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133435534</v>
+        <v>133437114</v>
       </c>
       <c r="B55" t="n">
-        <v>93256</v>
+        <v>79992</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Grelsmyran, Grelsmyran, Ång</t>
+          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>578265</v>
+        <v>578213</v>
       </c>
       <c r="R55" t="n">
-        <v>7069037</v>
+        <v>7069129</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6160,9 +6054,19 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6177,57 +6081,57 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133435901</v>
+        <v>133433425</v>
       </c>
       <c r="B56" t="n">
-        <v>79359</v>
+        <v>80382</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
+          <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>578190</v>
+        <v>578400</v>
       </c>
       <c r="R56" t="n">
-        <v>7069071</v>
+        <v>7068992</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6286,52 +6190,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133438494</v>
+        <v>133429440</v>
       </c>
       <c r="B57" t="n">
-        <v>99180</v>
+        <v>80488</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>578403</v>
+        <v>578440</v>
       </c>
       <c r="R57" t="n">
-        <v>7068788</v>
+        <v>7068786</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6358,9 +6258,19 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6375,22 +6285,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133430717</v>
+        <v>133429815</v>
       </c>
       <c r="B58" t="n">
-        <v>79359</v>
+        <v>80488</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6398,21 +6308,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6422,13 +6332,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>578436</v>
+        <v>578477</v>
       </c>
       <c r="R58" t="n">
-        <v>7068915</v>
+        <v>7068812</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6455,19 +6365,9 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>13:51</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6482,61 +6382,57 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133433530</v>
+        <v>133429833</v>
       </c>
       <c r="B59" t="n">
-        <v>99180</v>
+        <v>80488</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>578402</v>
+        <v>578453</v>
       </c>
       <c r="R59" t="n">
-        <v>7068986</v>
+        <v>7068845</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6568,7 +6464,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6578,7 +6474,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6605,10 +6501,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133436287</v>
+        <v>133429982</v>
       </c>
       <c r="B60" t="n">
-        <v>92230</v>
+        <v>80488</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6616,37 +6512,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
+          <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>578134</v>
+        <v>578431</v>
       </c>
       <c r="R60" t="n">
-        <v>7069094</v>
+        <v>7068866</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6673,9 +6569,19 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6690,22 +6596,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133434232</v>
+        <v>133430020</v>
       </c>
       <c r="B61" t="n">
-        <v>79359</v>
+        <v>80488</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6713,21 +6619,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6737,10 +6643,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>578401</v>
+        <v>578431</v>
       </c>
       <c r="R61" t="n">
-        <v>7069051</v>
+        <v>7068860</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6799,49 +6705,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133430079</v>
+        <v>133430065</v>
       </c>
       <c r="B62" t="n">
-        <v>99180</v>
+        <v>80488</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>578410</v>
+        <v>578420</v>
       </c>
       <c r="R62" t="n">
-        <v>7068853</v>
+        <v>7068858</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6900,10 +6802,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133437687</v>
+        <v>133430100</v>
       </c>
       <c r="B63" t="n">
-        <v>79359</v>
+        <v>80488</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6911,34 +6813,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
+          <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>578173</v>
+        <v>578414</v>
       </c>
       <c r="R63" t="n">
-        <v>7069031</v>
+        <v>7068843</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6997,10 +6899,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133430270</v>
+        <v>133430126</v>
       </c>
       <c r="B64" t="n">
-        <v>79359</v>
+        <v>80488</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7008,21 +6910,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7032,10 +6934,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>578405</v>
+        <v>578407</v>
       </c>
       <c r="R64" t="n">
-        <v>7068842</v>
+        <v>7068835</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7094,10 +6996,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133434509</v>
+        <v>133430367</v>
       </c>
       <c r="B65" t="n">
-        <v>80475</v>
+        <v>80488</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7105,21 +7007,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7129,10 +7031,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>578389</v>
+        <v>578383</v>
       </c>
       <c r="R65" t="n">
-        <v>7069082</v>
+        <v>7068819</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7164,7 +7066,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7174,7 +7076,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7201,10 +7103,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133435992</v>
+        <v>133430374</v>
       </c>
       <c r="B66" t="n">
-        <v>79359</v>
+        <v>80488</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7212,37 +7114,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
+          <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>578161</v>
+        <v>578394</v>
       </c>
       <c r="R66" t="n">
-        <v>7069056</v>
+        <v>7068863</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7269,19 +7171,9 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>14:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7296,22 +7188,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133429594</v>
+        <v>133431209</v>
       </c>
       <c r="B67" t="n">
-        <v>79359</v>
+        <v>80488</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7319,21 +7211,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7343,13 +7235,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>578438</v>
+        <v>578421</v>
       </c>
       <c r="R67" t="n">
-        <v>7068789</v>
+        <v>7068947</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7376,19 +7268,9 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:21</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7403,12 +7285,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7418,7 +7300,7 @@
         <v>133431244</v>
       </c>
       <c r="B68" t="n">
-        <v>80474</v>
+        <v>80488</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7512,10 +7394,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133432193</v>
+        <v>133432266</v>
       </c>
       <c r="B69" t="n">
-        <v>79359</v>
+        <v>80488</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7523,21 +7405,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7547,13 +7429,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>578384</v>
+        <v>578376</v>
       </c>
       <c r="R69" t="n">
-        <v>7068959</v>
+        <v>7068960</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7580,9 +7462,19 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7597,22 +7489,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133430100</v>
+        <v>133432869</v>
       </c>
       <c r="B70" t="n">
-        <v>80474</v>
+        <v>80488</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7644,13 +7536,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>578414</v>
+        <v>578371</v>
       </c>
       <c r="R70" t="n">
-        <v>7068843</v>
+        <v>7068956</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7677,9 +7569,19 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7694,22 +7596,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133429555</v>
+        <v>133433039</v>
       </c>
       <c r="B71" t="n">
-        <v>80475</v>
+        <v>80488</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7717,21 +7619,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7741,10 +7643,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>578443</v>
+        <v>578409</v>
       </c>
       <c r="R71" t="n">
-        <v>7068790</v>
+        <v>7068983</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7803,10 +7705,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133429701</v>
+        <v>133433493</v>
       </c>
       <c r="B72" t="n">
-        <v>91959</v>
+        <v>80488</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7814,21 +7716,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7838,10 +7740,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>578473</v>
+        <v>578396</v>
       </c>
       <c r="R72" t="n">
-        <v>7068808</v>
+        <v>7068978</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7900,32 +7802,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133434569</v>
+        <v>133433550</v>
       </c>
       <c r="B73" t="n">
-        <v>80485</v>
+        <v>80488</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7935,13 +7837,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>578370</v>
+        <v>578401</v>
       </c>
       <c r="R73" t="n">
-        <v>7069090</v>
+        <v>7068987</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7968,9 +7870,19 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7985,22 +7897,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133429815</v>
+        <v>133434517</v>
       </c>
       <c r="B74" t="n">
-        <v>80474</v>
+        <v>80488</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8032,10 +7944,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>578477</v>
+        <v>578367</v>
       </c>
       <c r="R74" t="n">
-        <v>7068812</v>
+        <v>7069089</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8094,10 +8006,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133438722</v>
+        <v>133434519</v>
       </c>
       <c r="B75" t="n">
-        <v>57975</v>
+        <v>80488</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8105,42 +8017,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>578437</v>
+        <v>578389</v>
       </c>
       <c r="R75" t="n">
-        <v>7068773</v>
+        <v>7069086</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8167,14 +8074,19 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8189,61 +8101,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133430678</v>
+        <v>133434892</v>
       </c>
       <c r="B76" t="n">
-        <v>99180</v>
+        <v>80488</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>578436</v>
+        <v>578330</v>
       </c>
       <c r="R76" t="n">
-        <v>7068908</v>
+        <v>7069066</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8275,7 +8183,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8285,7 +8193,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8312,10 +8220,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133434590</v>
+        <v>133436758</v>
       </c>
       <c r="B77" t="n">
-        <v>91959</v>
+        <v>80488</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8323,37 +8231,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Grelsmyran, Grelsmyran, Ång</t>
+          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>578381</v>
+        <v>578224</v>
       </c>
       <c r="R77" t="n">
-        <v>7069074</v>
+        <v>7069159</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8380,19 +8288,9 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>14:27</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8407,22 +8305,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133435652</v>
+        <v>133437707</v>
       </c>
       <c r="B78" t="n">
-        <v>79359</v>
+        <v>80488</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8430,21 +8328,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8454,10 +8352,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>578216</v>
+        <v>578156</v>
       </c>
       <c r="R78" t="n">
-        <v>7069068</v>
+        <v>7069028</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8489,7 +8387,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8499,7 +8397,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8526,10 +8424,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133429679</v>
+        <v>133438004</v>
       </c>
       <c r="B79" t="n">
-        <v>57975</v>
+        <v>80488</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8537,42 +8435,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Grelsmyran, Grelsmyran, Ång</t>
+          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>578446</v>
+        <v>578175</v>
       </c>
       <c r="R79" t="n">
-        <v>7068795</v>
+        <v>7068971</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8599,24 +8492,9 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8631,22 +8509,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133430367</v>
+        <v>133438634</v>
       </c>
       <c r="B80" t="n">
-        <v>80474</v>
+        <v>80488</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8678,13 +8556,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>578383</v>
+        <v>578399</v>
       </c>
       <c r="R80" t="n">
-        <v>7068819</v>
+        <v>7068800</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8711,19 +8589,9 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>13:43</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8738,44 +8606,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133430504</v>
+        <v>133434904</v>
       </c>
       <c r="B81" t="n">
-        <v>91959</v>
+        <v>80492</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8785,10 +8653,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>578403</v>
+        <v>578359</v>
       </c>
       <c r="R81" t="n">
-        <v>7068862</v>
+        <v>7069082</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8847,10 +8715,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133437423</v>
+        <v>133429944</v>
       </c>
       <c r="B82" t="n">
-        <v>93256</v>
+        <v>80493</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8858,34 +8726,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
+          <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>578202</v>
+        <v>578460</v>
       </c>
       <c r="R82" t="n">
-        <v>7069041</v>
+        <v>7068837</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8944,10 +8812,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133434576</v>
+        <v>133430112</v>
       </c>
       <c r="B83" t="n">
-        <v>80479</v>
+        <v>80493</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8979,10 +8847,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>578371</v>
+        <v>578414</v>
       </c>
       <c r="R83" t="n">
-        <v>7069089</v>
+        <v>7068843</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9041,32 +8909,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133438634</v>
+        <v>133431214</v>
       </c>
       <c r="B84" t="n">
-        <v>80474</v>
+        <v>80493</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9076,10 +8944,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>578399</v>
+        <v>578421</v>
       </c>
       <c r="R84" t="n">
-        <v>7068800</v>
+        <v>7068947</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9138,10 +9006,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133431214</v>
+        <v>133433500</v>
       </c>
       <c r="B85" t="n">
-        <v>80479</v>
+        <v>80493</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9173,10 +9041,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>578421</v>
+        <v>578397</v>
       </c>
       <c r="R85" t="n">
-        <v>7068947</v>
+        <v>7068978</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9235,32 +9103,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133430020</v>
+        <v>133434576</v>
       </c>
       <c r="B86" t="n">
-        <v>80474</v>
+        <v>80493</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9270,10 +9138,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>578431</v>
+        <v>578371</v>
       </c>
       <c r="R86" t="n">
-        <v>7068860</v>
+        <v>7069089</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9332,10 +9200,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133433500</v>
+        <v>133436792</v>
       </c>
       <c r="B87" t="n">
-        <v>80479</v>
+        <v>80493</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9363,14 +9231,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Grelsmyran, Grelsmyran, Ång</t>
+          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>578397</v>
+        <v>578224</v>
       </c>
       <c r="R87" t="n">
-        <v>7068978</v>
+        <v>7069161</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9429,32 +9297,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133430250</v>
+        <v>133434569</v>
       </c>
       <c r="B88" t="n">
-        <v>91955</v>
+        <v>80499</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9464,10 +9332,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>578387</v>
+        <v>578370</v>
       </c>
       <c r="R88" t="n">
-        <v>7068861</v>
+        <v>7069090</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9526,27 +9394,27 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133435402</v>
+        <v>133436778</v>
       </c>
       <c r="B89" t="n">
-        <v>79359</v>
+        <v>80499</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9557,14 +9425,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Grelsmyran, Grelsmyran, Ång</t>
+          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>578289</v>
+        <v>578226</v>
       </c>
       <c r="R89" t="n">
-        <v>7069077</v>
+        <v>7069160</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -9623,48 +9491,53 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133432574</v>
+        <v>133429129</v>
       </c>
       <c r="B90" t="n">
-        <v>91922</v>
+        <v>57975</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>578399</v>
+        <v>578422</v>
       </c>
       <c r="R90" t="n">
-        <v>7068956</v>
+        <v>7068785</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9691,9 +9564,24 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9708,22 +9596,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133433550</v>
+        <v>133429367</v>
       </c>
       <c r="B91" t="n">
-        <v>80474</v>
+        <v>57975</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9731,34 +9619,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>578401</v>
+        <v>578434</v>
       </c>
       <c r="R91" t="n">
-        <v>7068987</v>
+        <v>7068778</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9790,7 +9683,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -9800,7 +9693,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9827,10 +9725,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133437840</v>
+        <v>133429497</v>
       </c>
       <c r="B92" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9838,37 +9736,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
+          <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>578136</v>
+        <v>578428</v>
       </c>
       <c r="R92" t="n">
-        <v>7069035</v>
+        <v>7068775</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9895,19 +9798,14 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>15:39</t>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tre granar</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9922,22 +9820,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133434517</v>
+        <v>133429679</v>
       </c>
       <c r="B93" t="n">
-        <v>80474</v>
+        <v>57975</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9945,37 +9843,42 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>578367</v>
+        <v>578446</v>
       </c>
       <c r="R93" t="n">
-        <v>7069089</v>
+        <v>7068795</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10002,9 +9905,24 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10019,22 +9937,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133433999</v>
+        <v>133437836</v>
       </c>
       <c r="B94" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10042,34 +9960,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Grelsmyran, Grelsmyran, Ång</t>
+          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>578377</v>
+        <v>578155</v>
       </c>
       <c r="R94" t="n">
-        <v>7068960</v>
+        <v>7069003</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10102,6 +10025,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10128,10 +10056,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133434766</v>
+        <v>133437986</v>
       </c>
       <c r="B95" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10139,34 +10067,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Grelsmyran, Grelsmyran, Ång</t>
+          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>578368</v>
+        <v>578166</v>
       </c>
       <c r="R95" t="n">
-        <v>7069064</v>
+        <v>7068960</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10199,6 +10132,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10225,10 +10163,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133437851</v>
+        <v>133437997</v>
       </c>
       <c r="B96" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10236,37 +10174,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>578141</v>
+        <v>578178</v>
       </c>
       <c r="R96" t="n">
-        <v>7069003</v>
+        <v>7068977</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10293,9 +10236,24 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10310,49 +10268,50 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133437652</v>
+        <v>133438077</v>
       </c>
       <c r="B97" t="n">
-        <v>99180</v>
+        <v>57975</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -10361,13 +10320,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>578182</v>
+        <v>578189</v>
       </c>
       <c r="R97" t="n">
-        <v>7069031</v>
+        <v>7068967</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10394,9 +10353,24 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10411,22 +10385,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133433950</v>
+        <v>133438237</v>
       </c>
       <c r="B98" t="n">
-        <v>83208</v>
+        <v>57975</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10434,37 +10408,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>578437</v>
+        <v>578345</v>
       </c>
       <c r="R98" t="n">
-        <v>7068980</v>
+        <v>7068862</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10491,19 +10470,14 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>14:17</t>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10518,22 +10492,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133432171</v>
+        <v>133438270</v>
       </c>
       <c r="B99" t="n">
-        <v>83208</v>
+        <v>57975</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10541,34 +10515,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>578390</v>
+        <v>578349</v>
       </c>
       <c r="R99" t="n">
-        <v>7068946</v>
+        <v>7068845</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10600,7 +10579,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10610,7 +10589,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10637,7 +10621,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133438392</v>
+        <v>133438295</v>
       </c>
       <c r="B100" t="n">
         <v>57975</v>
@@ -10677,10 +10661,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>578366</v>
+        <v>578362</v>
       </c>
       <c r="R100" t="n">
-        <v>7068811</v>
+        <v>7068822</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10744,7 +10728,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133438472</v>
+        <v>133438392</v>
       </c>
       <c r="B101" t="n">
         <v>57975</v>
@@ -10784,10 +10768,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>578380</v>
+        <v>578366</v>
       </c>
       <c r="R101" t="n">
-        <v>7068797</v>
+        <v>7068811</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10851,10 +10835,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133435661</v>
+        <v>133438434</v>
       </c>
       <c r="B102" t="n">
-        <v>78762</v>
+        <v>57975</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10862,37 +10846,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
+          <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>578205</v>
+        <v>578368</v>
       </c>
       <c r="R102" t="n">
-        <v>7069057</v>
+        <v>7068807</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10919,9 +10908,24 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10936,49 +10940,50 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133430269</v>
+        <v>133438451</v>
       </c>
       <c r="B103" t="n">
-        <v>99180</v>
+        <v>57975</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -10987,13 +10992,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>578383</v>
+        <v>578375</v>
       </c>
       <c r="R103" t="n">
-        <v>7068846</v>
+        <v>7068798</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11020,19 +11025,14 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>13:40</t>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11047,22 +11047,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133431175</v>
+        <v>133438472</v>
       </c>
       <c r="B104" t="n">
-        <v>79116</v>
+        <v>57975</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11070,37 +11070,42 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>578457</v>
+        <v>578380</v>
       </c>
       <c r="R104" t="n">
-        <v>7068932</v>
+        <v>7068797</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11127,19 +11132,14 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>13:54</t>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11154,22 +11154,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133434519</v>
+        <v>133438615</v>
       </c>
       <c r="B105" t="n">
-        <v>80474</v>
+        <v>57975</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11177,37 +11177,42 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>578389</v>
+        <v>578397</v>
       </c>
       <c r="R105" t="n">
-        <v>7069086</v>
+        <v>7068804</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11234,19 +11239,14 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>14:25</t>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11261,22 +11261,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133429833</v>
+        <v>133438722</v>
       </c>
       <c r="B106" t="n">
-        <v>80474</v>
+        <v>57975</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11284,37 +11284,42 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>578453</v>
+        <v>578437</v>
       </c>
       <c r="R106" t="n">
-        <v>7068845</v>
+        <v>7068773</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11341,19 +11346,14 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>13:25</t>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11368,22 +11368,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133434261</v>
+        <v>133438750</v>
       </c>
       <c r="B107" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11391,37 +11391,42 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>578409</v>
+        <v>578442</v>
       </c>
       <c r="R107" t="n">
-        <v>7069061</v>
+        <v>7068773</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11448,19 +11453,14 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>14:23</t>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11475,49 +11475,50 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133434878</v>
+        <v>133438778</v>
       </c>
       <c r="B108" t="n">
-        <v>99180</v>
+        <v>57975</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -11526,13 +11527,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>578355</v>
+        <v>578454</v>
       </c>
       <c r="R108" t="n">
-        <v>7069073</v>
+        <v>7068761</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11559,19 +11560,14 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>14:32</t>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11586,60 +11582,64 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133431225</v>
+        <v>133429860</v>
       </c>
       <c r="B109" t="n">
-        <v>79359</v>
+        <v>99195</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>578436</v>
+        <v>578479</v>
       </c>
       <c r="R109" t="n">
-        <v>7068937</v>
+        <v>7068822</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11666,19 +11666,9 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>13:55</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11693,60 +11683,64 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133429440</v>
+        <v>133429893</v>
       </c>
       <c r="B110" t="n">
-        <v>80474</v>
+        <v>99195</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>578440</v>
+        <v>578469</v>
       </c>
       <c r="R110" t="n">
-        <v>7068786</v>
+        <v>7068830</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11773,19 +11767,9 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11800,50 +11784,49 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>133429129</v>
+        <v>133429928</v>
       </c>
       <c r="B111" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>500</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -11852,10 +11835,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>578422</v>
+        <v>578452</v>
       </c>
       <c r="R111" t="n">
-        <v>7068785</v>
+        <v>7068835</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11887,7 +11870,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -11897,12 +11880,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11929,10 +11907,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>133429860</v>
+        <v>133430079</v>
       </c>
       <c r="B112" t="n">
-        <v>99180</v>
+        <v>99195</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11959,7 +11937,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -11968,10 +11946,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>578479</v>
+        <v>578410</v>
       </c>
       <c r="R112" t="n">
-        <v>7068822</v>
+        <v>7068853</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -12030,48 +12008,52 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>133433425</v>
+        <v>133430269</v>
       </c>
       <c r="B113" t="n">
-        <v>80368</v>
+        <v>99195</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>578400</v>
+        <v>578383</v>
       </c>
       <c r="R113" t="n">
-        <v>7068992</v>
+        <v>7068846</v>
       </c>
       <c r="S113" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12098,9 +12080,19 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12115,60 +12107,64 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>133430126</v>
+        <v>133430678</v>
       </c>
       <c r="B114" t="n">
-        <v>80474</v>
+        <v>99195</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>578407</v>
+        <v>578436</v>
       </c>
       <c r="R114" t="n">
-        <v>7068835</v>
+        <v>7068908</v>
       </c>
       <c r="S114" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12195,9 +12191,19 @@
           <t>2026-05-14</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12212,57 +12218,61 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>133430112</v>
+        <v>133430713</v>
       </c>
       <c r="B115" t="n">
-        <v>80479</v>
+        <v>99195</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>578414</v>
+        <v>578421</v>
       </c>
       <c r="R115" t="n">
-        <v>7068843</v>
+        <v>7068942</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12321,48 +12331,52 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>133437707</v>
+        <v>133432167</v>
       </c>
       <c r="B116" t="n">
-        <v>80474</v>
+        <v>99195</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
+          <t>Grelsmyran, Grelsmyran, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>578156</v>
+        <v>578386</v>
       </c>
       <c r="R116" t="n">
-        <v>7069028</v>
+        <v>7068948</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12389,19 +12403,9 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>15:37</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>15:37</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12416,50 +12420,49 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>133438434</v>
+        <v>133433530</v>
       </c>
       <c r="B117" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -12468,10 +12471,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>578368</v>
+        <v>578402</v>
       </c>
       <c r="R117" t="n">
-        <v>7068807</v>
+        <v>7068986</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12503,7 +12506,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12513,12 +12516,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>15:56</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12542,6 +12540,513 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>133434878</v>
+      </c>
+      <c r="B118" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Grelsmyran, Grelsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>578355</v>
+      </c>
+      <c r="R118" t="n">
+        <v>7069073</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>133437652</v>
+      </c>
+      <c r="B119" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>578182</v>
+      </c>
+      <c r="R119" t="n">
+        <v>7069031</v>
+      </c>
+      <c r="S119" t="n">
+        <v>15</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>133438494</v>
+      </c>
+      <c r="B120" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Grelsmyran, Grelsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>578403</v>
+      </c>
+      <c r="R120" t="n">
+        <v>7068788</v>
+      </c>
+      <c r="S120" t="n">
+        <v>15</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>133436474</v>
+      </c>
+      <c r="B121" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>578142</v>
+      </c>
+      <c r="R121" t="n">
+        <v>7069100</v>
+      </c>
+      <c r="S121" t="n">
+        <v>15</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>133436377</v>
+      </c>
+      <c r="B122" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Små-Göktjärnarna, Små-Göktjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>578125</v>
+      </c>
+      <c r="R122" t="n">
+        <v>7069083</v>
+      </c>
+      <c r="S122" t="n">
+        <v>15</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
